--- a/site/exports/xjtu-public-policy-management.xlsx
+++ b/site/exports/xjtu-public-policy-management.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,18 +443,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18.2" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,65 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>吕书鹏</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>公共政策与管理学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=2714</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期未单独记录）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>单一官方职业履历支持部分候选；未独立读取具名师资目录，目录归属未核。；页面更新标记不等于现时人事核验；当前在职未知。；没有本人导师关系证据；不把博导职称或共同作者当作本人导师。；只保留必要职业摘录，不声称保存原始完整HTTP。；四项学历/学位标签不是明确获授句；均保留 degree_awarded=null。第二学位辅修不推断实际获授。；两项作品来自履历，未外核出版元数据及全文；星号含义不推断。；来源记载职业信息：职业职称：长聘副教授/博导。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,11 +692,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -720,7 +774,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1259,8 +1313,471 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>吕书鹏</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>study_label_award_unknown</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>哲学博士</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>香港中文大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2012-10</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>政治与行政学</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：博士</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=2714</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>吕书鹏</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>study_label_award_unknown</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>管理学硕士</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2007-09</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2009-06</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>公共管理</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：硕士</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=2714</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>吕书鹏</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>study_label_award_unknown</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>文学第二学位辅修</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2005-02</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2006-10</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：第二学位辅修</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=2714</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>吕书鹏</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>study_label_award_unknown</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>管理学学士</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2003-09</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2007-06</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>行政管理</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：本科</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=2714</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>吕书鹏</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>美国堪萨斯大学</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2017-05</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>非学位职业/研修阶段；不否定其既有博士资格。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（院系）：文理学院；来源记载（event_kind）：访问学者</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=2714</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>吕书鹏</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2015-09</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>非学位职业/研修阶段；不否定其既有博士资格。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（院系）：政府管理学院；来源记载（event_kind）：博士后</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=2714</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>吕书鹏</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>讲师，硕士生导师</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2015-09</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（院系）：公共政策与管理学院</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=2714</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S9"/>
+  <autoFilter ref="A1:S16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1270,6 +1787,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1372,18 +1896,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="44.8" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="60.2" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="60.2" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="62.99999999999999" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1555,13 +2079,121 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>吕书鹏</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>中外政治思想史纲</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=2714</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=2714</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：吕书鹏、袁志东</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>吕书鹏</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>差序政府信任：概念、现状及成因——基于三次全国调查数据的实证研究</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=2714</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=2714</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：吕书鹏；来源书目信息（期）：第4期</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1573,11 +2205,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="33.59999999999999" customWidth="1" min="2" max="2"/>
+    <col width="62.99999999999999" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -1766,13 +2398,47 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>吕书鹏</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-xjtu-lvshupeng-s001-0d56c325d1d2</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=2714</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/xjtu-public-policy-management.xlsx
+++ b/site/exports/xjtu-public-policy-management.xlsx
@@ -1423,7 +1423,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1685,7 +1685,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L15" s="2" t="b">
